--- a/data/trans_bre/IP04D$notiene-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Provincia-trans_bre.xlsx
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -632,39 +632,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 6,96</t>
+          <t>-15,59; 9,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 3,62</t>
+          <t>-26,06; 2,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 35,91</t>
+          <t>3,81; 36,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 53,36</t>
+          <t>-59,09; 69,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 7,4</t>
+          <t>-45,34; 5,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 196,92</t>
+          <t>9,77; 204,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,39 +712,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,77</t>
+          <t>-5,1; 7,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 4,32</t>
+          <t>-14,49; 4,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 0,71</t>
+          <t>-12,77; 0,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 190,05</t>
+          <t>-52,29; 197,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 19,98</t>
+          <t>-46,39; 17,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,84; 19,65</t>
+          <t>-84,32; 23,86</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,22</t>
+          <t>-2,01; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 8,64</t>
+          <t>-0,79; 8,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,75</t>
+          <t>-4,3; 4,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,67</t>
+          <t>0,82; 7,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 0,41</t>
+          <t>-11,92; 0,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 3,96</t>
+          <t>-7,85; 4,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,21</t>
+          <t>-100,0; 82,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 9,31</t>
+          <t>-7,12; 9,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 12,17</t>
+          <t>-14,38; 13,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 8,8</t>
+          <t>-0,8; 8,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 67,81</t>
+          <t>-42,98; 72,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,4</t>
+          <t>-4,1; 1,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 10,53</t>
+          <t>-4,77; 9,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 3,57</t>
+          <t>-18,82; 4,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,0</t>
+          <t>-89,68; 218,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 82,33</t>
+          <t>-23,49; 72,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 9,96</t>
+          <t>-38,77; 12,63</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,14</t>
+          <t>-1,27; 3,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,34</t>
+          <t>-2,48; 0,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,11</t>
+          <t>-1,53; 4,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-81,82; 838,41</t>
+          <t>-80,57; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,07; 957,25</t>
+          <t>-75,66; 757,72</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,71</t>
+          <t>-1,92; 1,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,19</t>
+          <t>-4,98; 1,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,53</t>
+          <t>-4,57; 3,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 55,38</t>
+          <t>-38,37; 55,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 8,85</t>
+          <t>-30,4; 9,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 30,14</t>
+          <t>-29,15; 28,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Provincia-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 9,02</t>
+          <t>-17,17; 7,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 2,27</t>
+          <t>-25,52; 3,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 36,22</t>
+          <t>4,1; 37,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-59,09; 69,55</t>
+          <t>-61,73; 56,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 5,03</t>
+          <t>-44,02; 8,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 204,0</t>
+          <t>6,28; 226,74</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 7,88</t>
+          <t>-5,22; 7,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 4,23</t>
+          <t>-14,32; 3,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 0,62</t>
+          <t>-12,9; 1,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 197,02</t>
+          <t>-52,26; 188,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 17,35</t>
+          <t>-45,82; 15,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,32; 23,86</t>
+          <t>-84,3; 19,1</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,29</t>
+          <t>-2,04; 3,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 8,14</t>
+          <t>-0,84; 8,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,46</t>
+          <t>-3,86; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,05</t>
+          <t>0,8; 7,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 0,43</t>
+          <t>-10,87; 0,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 4,1</t>
+          <t>-8,47; 3,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,82</t>
+          <t>-100,0; 70,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 9,45</t>
+          <t>-6,86; 9,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 13,56</t>
+          <t>-15,85; 14,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 8,8</t>
+          <t>-0,9; 10,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 72,28</t>
+          <t>-46,0; 77,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,63</t>
+          <t>-4,9; 1,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 9,79</t>
+          <t>-4,11; 10,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 4,44</t>
+          <t>-19,22; 4,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-89,68; 218,03</t>
+          <t>-100,0; 195,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 72,89</t>
+          <t>-21,45; 77,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 12,63</t>
+          <t>-38,56; 14,37</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,25</t>
+          <t>-1,57; 3,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,33</t>
+          <t>-3,1; 0,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,26</t>
+          <t>-1,32; 4,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,57; —</t>
+          <t>-86,11; 1030,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,66; 757,72</t>
+          <t>-73,96; 641,43</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,75</t>
+          <t>-1,79; 1,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,24</t>
+          <t>-4,82; 1,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,53</t>
+          <t>-4,43; 3,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 55,49</t>
+          <t>-36,55; 51,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,73</t>
+          <t>-28,7; 7,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 28,82</t>
+          <t>-28,99; 30,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Provincia-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>10,14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 7,03</t>
+          <t>-14,95; 6,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 3,84</t>
+          <t>-26,08; 3,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 37,74</t>
+          <t>-2,89; 22,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 56,5</t>
+          <t>-59,1; 53,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 8,57</t>
+          <t>-44,2; 7,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 226,74</t>
+          <t>-11,13; 137,03</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,38</t>
+          <t>-4,89</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-51,52%</t>
+          <t>-45,89%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 7,87</t>
+          <t>-5,23; 7,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 3,43</t>
+          <t>-13,89; 4,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 1,25</t>
+          <t>-11,42; 1,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 188,73</t>
+          <t>-50,91; 190,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 15,13</t>
+          <t>-44,1; 19,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,3; 19,1</t>
+          <t>-77,87; 31,33</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,73%</t>
+          <t>-10,9%</t>
         </is>
       </c>
     </row>
@@ -792,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,25</t>
+          <t>-2,03; 4,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,34</t>
+          <t>-0,71; 8,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 5,55</t>
+          <t>-4,14; 4,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,7%</t>
+          <t>-38,41%</t>
         </is>
       </c>
     </row>
@@ -872,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,41</t>
+          <t>0,82; 7,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 0,68</t>
+          <t>-11,63; 0,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 3,48</t>
+          <t>-8,07; 3,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -892,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,47</t>
+          <t>-100,0; 42,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -952,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 9,31</t>
+          <t>-6,59; 9,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -967,7 +969,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>270,8%</t>
+          <t>234,89%</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 14,12</t>
+          <t>-16,18; 12,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,35</t>
+          <t>-1,13; 9,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1052,7 +1054,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 77,57</t>
+          <t>-45,72; 67,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,0</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-16,77%</t>
+          <t>-6,3%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,38</t>
+          <t>-4,12; 1,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 10,16</t>
+          <t>-4,67; 10,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 4,9</t>
+          <t>-13,06; 7,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 195,02</t>
+          <t>-100,0; 188,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 77,9</t>
+          <t>-24,42; 82,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 14,37</t>
+          <t>-30,83; 23,82</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1179,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1194,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,41</t>
+          <t>-1,23; 3,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,27</t>
+          <t>-2,83; 0,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,27</t>
+          <t>-1,57; 4,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-86,11; 1030,29</t>
+          <t>-81,82; 838,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1217,7 +1219,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,96; 641,43</t>
+          <t>-74,83; 1085,43</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1259,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-2,77%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,6</t>
+          <t>-1,89; 1,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,08</t>
+          <t>-4,68; 1,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,62</t>
+          <t>-3,45; 2,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 51,7</t>
+          <t>-36,56; 55,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 7,65</t>
+          <t>-28,75; 8,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 30,35</t>
+          <t>-24,45; 26,1</t>
         </is>
       </c>
     </row>
